--- a/artfynd/A 67861-2019 artfynd.xlsx
+++ b/artfynd/A 67861-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67861-2019 artfynd.xlsx
+++ b/artfynd/A 67861-2019 artfynd.xlsx
@@ -13299,7 +13299,7 @@
         <v>126843566</v>
       </c>
       <c r="B112" t="n">
-        <v>79047</v>
+        <v>79078</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>126843563</v>
       </c>
       <c r="B113" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>126843570</v>
       </c>
       <c r="B114" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>126843561</v>
       </c>
       <c r="B115" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>126843571</v>
       </c>
       <c r="B116" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
